--- a/E/RBI01S.xlsx
+++ b/E/RBI01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="105">
   <si>
     <t/>
   </si>
@@ -217,7 +217,7 @@
     <t>20117327</t>
   </si>
   <si>
-    <t xml:space="preserve">BUAH POT JRK NAVEL </t>
+    <t>BUAH POT JRK NAVEL</t>
   </si>
   <si>
     <t>PT,(E-1J)</t>
@@ -302,6 +302,15 @@
   </si>
   <si>
     <t>APEL CHERRY/STRAWBRY</t>
+  </si>
+  <si>
+    <t>20117282</t>
+  </si>
+  <si>
+    <t>PEAR PAKAM PCK</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>20112666</t>
@@ -709,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1439,7 +1448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -1450,10 +1459,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1467,9 +1479,26 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/E/RBI01S.xlsx
+++ b/E/RBI01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="117">
   <si>
     <t/>
   </si>
@@ -223,75 +223,63 @@
     <t>PT,(E-1J)</t>
   </si>
   <si>
-    <t>20111887</t>
-  </si>
-  <si>
-    <t>OLAH P XIANG BAZ WHL</t>
-  </si>
-  <si>
-    <t>20117343</t>
-  </si>
-  <si>
-    <t>POT P XIANG BAZ PCK</t>
+    <t>20117340</t>
+  </si>
+  <si>
+    <t>POT PEAR SW BAZ PCK</t>
+  </si>
+  <si>
+    <t>20117345</t>
+  </si>
+  <si>
+    <t>POT APEL FJ BAZ PCK</t>
+  </si>
+  <si>
+    <t>20137134</t>
+  </si>
+  <si>
+    <t>JERUK IMP PCK</t>
+  </si>
+  <si>
+    <t>20111884</t>
+  </si>
+  <si>
+    <t>POT PEAR SW BAZ WHL</t>
+  </si>
+  <si>
+    <t>20138452</t>
+  </si>
+  <si>
+    <t>OLAH PEAR CENT WHL</t>
+  </si>
+  <si>
+    <t>20138455</t>
+  </si>
+  <si>
+    <t>OLAH CAMPUR IMP WHL</t>
+  </si>
+  <si>
+    <t>20111812</t>
+  </si>
+  <si>
+    <t>BUAH PT PEAR CEN PCS</t>
+  </si>
+  <si>
+    <t>20093014</t>
+  </si>
+  <si>
+    <t>POT CAMPUR IMP PCK</t>
+  </si>
+  <si>
+    <t>20139147</t>
+  </si>
+  <si>
+    <t>B/O JERUK SUNKIST CR</t>
   </si>
   <si>
     <t>,(E-1J)</t>
   </si>
   <si>
-    <t>20117340</t>
-  </si>
-  <si>
-    <t>POT PEAR SW BAZ PCK</t>
-  </si>
-  <si>
-    <t>20117345</t>
-  </si>
-  <si>
-    <t>POT APEL FJ BAZ PCK</t>
-  </si>
-  <si>
-    <t>20137134</t>
-  </si>
-  <si>
-    <t>JERUK IMP PCK</t>
-  </si>
-  <si>
-    <t>20111884</t>
-  </si>
-  <si>
-    <t>POT PEAR SW BAZ WHL</t>
-  </si>
-  <si>
-    <t>20138452</t>
-  </si>
-  <si>
-    <t>OLAH PEAR CENT WHL</t>
-  </si>
-  <si>
-    <t>20138455</t>
-  </si>
-  <si>
-    <t>OLAH CAMPUR IMP WHL</t>
-  </si>
-  <si>
-    <t>20111812</t>
-  </si>
-  <si>
-    <t>BUAH PT PEAR CEN PCS</t>
-  </si>
-  <si>
-    <t>20093014</t>
-  </si>
-  <si>
-    <t>POT CAMPUR IMP PCK</t>
-  </si>
-  <si>
-    <t>20139147</t>
-  </si>
-  <si>
-    <t>B/O JERUK SUNKIST CR</t>
-  </si>
-  <si>
     <t>20139149</t>
   </si>
   <si>
@@ -311,6 +299,54 @@
   </si>
   <si>
     <t>18</t>
+  </si>
+  <si>
+    <t>20142369</t>
+  </si>
+  <si>
+    <t>PEAR SINGO  PCK</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20131584</t>
+  </si>
+  <si>
+    <t>ANGGUR RD FELIPE PCK</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>,(E-1H)</t>
+  </si>
+  <si>
+    <t>10002531</t>
+  </si>
+  <si>
+    <t>JERUK BABY WOGAN</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20142371</t>
+  </si>
+  <si>
+    <t>JERUK MANDARIN PCK</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20142370</t>
+  </si>
+  <si>
+    <t>PEAR GOLDEN  PCK</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t>20112666</t>
@@ -718,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1202,10 +1238,10 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1222,19 +1258,19 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
@@ -1242,19 +1278,19 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
@@ -1262,19 +1298,19 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1282,19 +1318,19 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1338,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>30</v>
@@ -1310,11 +1346,11 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
@@ -1322,19 +1358,19 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
@@ -1342,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>30</v>
@@ -1350,22 +1386,22 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1382,10 +1418,10 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1402,10 +1438,10 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1422,18 +1458,18 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1442,7 +1478,7 @@
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1450,10 +1486,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1462,43 +1498,103 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/E/RBI01S.xlsx
+++ b/E/RBI01S.xlsx
@@ -238,7 +238,7 @@
     <t>20137134</t>
   </si>
   <si>
-    <t>JERUK IMP PCK</t>
+    <t>JERUK IMPORT PCK</t>
   </si>
   <si>
     <t>20111884</t>

--- a/E/RBI01S.xlsx
+++ b/E/RBI01S.xlsx
@@ -52,7 +52,7 @@
     <t>10007668</t>
   </si>
   <si>
-    <t>JRK SANTANG BAZ WHL</t>
+    <t>JRK BABY SANTANG BZR</t>
   </si>
   <si>
     <t>4</t>
@@ -70,7 +70,7 @@
     <t>10038069</t>
   </si>
   <si>
-    <t>LENGKENG BKK BAZ WHL</t>
+    <t>LENGKENG BANGKOK BZR</t>
   </si>
   <si>
     <t>6</t>
@@ -190,7 +190,7 @@
     <t>20130892</t>
   </si>
   <si>
-    <t xml:space="preserve">AGR MUSCAT H PCK </t>
+    <t>AGR SHINE MSCT BAZAR</t>
   </si>
   <si>
     <t>20</t>

--- a/E/RBI01S.xlsx
+++ b/E/RBI01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="116">
   <si>
     <t/>
   </si>
@@ -298,28 +298,25 @@
     <t>PEAR PAKAM PCK</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>20142369</t>
   </si>
   <si>
     <t>PEAR SINGO  PCK</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>20131584</t>
   </si>
   <si>
-    <t>ANGGUR RD FELIPE PCK</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>,(E-1H)</t>
+    <t>ANGGUR RD PCK</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
   </si>
   <si>
     <t>10002531</t>
@@ -328,7 +325,7 @@
     <t>JERUK BABY WOGAN</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>20142371</t>
@@ -337,7 +334,7 @@
     <t>JERUK MANDARIN PCK</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>20142370</t>
@@ -346,7 +343,7 @@
     <t>PEAR GOLDEN  PCK</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>20112666</t>
@@ -355,7 +352,7 @@
     <t>TRAY BUAH PTNG IMP</t>
   </si>
   <si>
-    <t>50</t>
+    <t>998</t>
   </si>
   <si>
     <t>20112665</t>
@@ -760,7 +757,8 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1318,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>30</v>
@@ -1338,7 +1336,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>30</v>
@@ -1358,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>69</v>
@@ -1378,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>30</v>
@@ -1398,7 +1396,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>88</v>
@@ -1418,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>69</v>
@@ -1438,7 +1436,7 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1458,7 +1456,7 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1466,19 +1464,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1486,39 +1484,39 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1526,19 +1524,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1546,19 +1544,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1566,16 +1564,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>4</v>
@@ -1583,16 +1581,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>8</v>

--- a/E/RBI01S.xlsx
+++ b/E/RBI01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="110">
   <si>
     <t/>
   </si>
@@ -94,27 +94,18 @@
     <t>8</t>
   </si>
   <si>
-    <t>20111882</t>
-  </si>
-  <si>
-    <t>BUAH OLAH ANGGUR WHL</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>20111891</t>
+  </si>
+  <si>
+    <t>POT APEL FJ BAZ WHL</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>,(E-2J)</t>
   </si>
   <si>
-    <t>20111891</t>
-  </si>
-  <si>
-    <t>POT APEL FJ BAZ WHL</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>20056609</t>
   </si>
   <si>
@@ -253,12 +244,6 @@
     <t>OLAH PEAR CENT WHL</t>
   </si>
   <si>
-    <t>20138455</t>
-  </si>
-  <si>
-    <t>OLAH CAMPUR IMP WHL</t>
-  </si>
-  <si>
     <t>20111812</t>
   </si>
   <si>
@@ -314,9 +299,6 @@
   </si>
   <si>
     <t>25</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
   </si>
   <si>
     <t>10002531</t>
@@ -751,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -979,7 +961,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1179,7 +1161,7 @@
         <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1193,13 +1175,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1216,19 +1198,19 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
@@ -1236,19 +1218,19 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
@@ -1256,19 +1238,19 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
@@ -1276,19 +1258,19 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
@@ -1296,7 +1278,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>30</v>
@@ -1304,11 +1286,11 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1316,19 +1298,19 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
@@ -1336,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>30</v>
@@ -1344,22 +1326,22 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,10 +1358,10 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1396,19 +1378,19 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
@@ -1416,27 +1398,27 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1456,7 +1438,7 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1464,10 +1446,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1476,7 +1458,7 @@
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1484,10 +1466,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1496,10 +1478,10 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1522,7 +1504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>105</v>
       </c>
@@ -1533,16 +1515,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>108</v>
       </c>
@@ -1553,46 +1532,9 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E42" s="1" t="s">
         <v>8</v>
       </c>
     </row>
